--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_NÁUTICO TENERIFE.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_NÁUTICO TENERIFE.xlsx
@@ -565,13 +565,13 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>70.5518</v>
+        <v>65.3318</v>
       </c>
       <c r="E2" t="n">
-        <v>37.0102</v>
+        <v>33.0876</v>
       </c>
       <c r="F2" t="n">
-        <v>33.5416</v>
+        <v>32.2437</v>
       </c>
       <c r="G2" t="n">
         <v>32.3938</v>
@@ -610,13 +610,13 @@
         <v>53.2892</v>
       </c>
       <c r="S2" t="n">
-        <v>8.6068</v>
+        <v>3.3865</v>
       </c>
       <c r="T2" t="n">
-        <v>6.415700000000001</v>
+        <v>2.4931</v>
       </c>
       <c r="U2" t="n">
-        <v>2.191</v>
+        <v>0.8934000000000002</v>
       </c>
       <c r="V2" t="n">
         <v>-2.1136</v>
@@ -643,13 +643,13 @@
         <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>60.09979999999999</v>
+        <v>60.386</v>
       </c>
       <c r="E3" t="n">
-        <v>37.0583</v>
+        <v>38.4788</v>
       </c>
       <c r="F3" t="n">
-        <v>23.0419</v>
+        <v>21.9068</v>
       </c>
       <c r="G3" t="n">
         <v>16.785</v>
@@ -688,13 +688,13 @@
         <v>64.10169999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8038</v>
+        <v>3.0897</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6471999999999998</v>
+        <v>0.7736000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>3.4514</v>
+        <v>2.3166</v>
       </c>
       <c r="V3" t="n">
         <v>46.8823</v>
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>41.7059</v>
+        <v>38.34070000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>26.7063</v>
+        <v>23.4105</v>
       </c>
       <c r="F4" t="n">
-        <v>14.9999</v>
+        <v>14.9301</v>
       </c>
       <c r="G4" t="n">
         <v>40.6658</v>
@@ -766,13 +766,13 @@
         <v>59.275</v>
       </c>
       <c r="S4" t="n">
-        <v>9.6533</v>
+        <v>6.2885</v>
       </c>
       <c r="T4" t="n">
-        <v>7.7943</v>
+        <v>4.4991</v>
       </c>
       <c r="U4" t="n">
-        <v>1.8591</v>
+        <v>1.7895</v>
       </c>
       <c r="V4" t="n">
         <v>-6.8758</v>
@@ -799,13 +799,13 @@
         <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>26.0292</v>
+        <v>24.7893</v>
       </c>
       <c r="E5" t="n">
-        <v>15.537</v>
+        <v>14.5376</v>
       </c>
       <c r="F5" t="n">
-        <v>10.4923</v>
+        <v>10.2516</v>
       </c>
       <c r="G5" t="n">
         <v>3.4983</v>
@@ -844,13 +844,13 @@
         <v>25.4862</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6467</v>
+        <v>2.4067</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0357</v>
+        <v>1.036</v>
       </c>
       <c r="U5" t="n">
-        <v>1.611</v>
+        <v>1.3708</v>
       </c>
       <c r="V5" t="n">
         <v>7.2997</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GARCIA GARCIA</t>
+          <t>J. GONZÁLEZ CHÁVEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>24.5077</v>
+        <v>19.6645</v>
       </c>
       <c r="E6" t="n">
-        <v>14.6862</v>
+        <v>6.0669</v>
       </c>
       <c r="F6" t="n">
-        <v>9.821100000000001</v>
+        <v>13.5978</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.8115</v>
+        <v>5.848599999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-7.4935</v>
+        <v>-1.7428</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6818</v>
+        <v>7.5914</v>
       </c>
       <c r="J6" t="n">
-        <v>12.1049</v>
+        <v>9.197500000000002</v>
       </c>
       <c r="K6" t="n">
-        <v>7.212300000000001</v>
+        <v>1.16</v>
       </c>
       <c r="L6" t="n">
-        <v>4.893</v>
+        <v>8.0374</v>
       </c>
       <c r="M6" t="n">
-        <v>-15.9164</v>
+        <v>-3.3488</v>
       </c>
       <c r="N6" t="n">
-        <v>-14.7056</v>
+        <v>-2.9028</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.211100000000001</v>
+        <v>-0.4459999999999997</v>
       </c>
       <c r="P6" t="n">
-        <v>15.4462</v>
+        <v>3.861499999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>-28.3828</v>
+        <v>-15.2532</v>
       </c>
       <c r="R6" t="n">
-        <v>43.8289</v>
+        <v>19.1147</v>
       </c>
       <c r="S6" t="n">
-        <v>5.9682</v>
+        <v>-0.3581</v>
       </c>
       <c r="T6" t="n">
-        <v>11.5469</v>
+        <v>-0.555</v>
       </c>
       <c r="U6" t="n">
-        <v>-5.5787</v>
+        <v>0.1969</v>
       </c>
       <c r="V6" t="n">
-        <v>6.905</v>
+        <v>10.3126</v>
       </c>
       <c r="W6" t="n">
-        <v>19.4171</v>
+        <v>12.6776</v>
       </c>
       <c r="X6" t="n">
-        <v>-12.5121</v>
+        <v>-2.365</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GONZÁLEZ CHÁVEZ</t>
+          <t>J. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>16.2777</v>
+        <v>17.2848</v>
       </c>
       <c r="E7" t="n">
-        <v>3.557000000000001</v>
+        <v>6.6614</v>
       </c>
       <c r="F7" t="n">
-        <v>12.7207</v>
+        <v>10.6238</v>
       </c>
       <c r="G7" t="n">
-        <v>5.848599999999999</v>
+        <v>-3.8115</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.7428</v>
+        <v>-7.4935</v>
       </c>
       <c r="I7" t="n">
-        <v>7.5914</v>
+        <v>3.6818</v>
       </c>
       <c r="J7" t="n">
-        <v>9.197500000000002</v>
+        <v>12.1049</v>
       </c>
       <c r="K7" t="n">
-        <v>1.16</v>
+        <v>7.212300000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>8.0374</v>
+        <v>4.893</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.3488</v>
+        <v>-15.9164</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.9028</v>
+        <v>-14.7056</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4459999999999997</v>
+        <v>-1.211100000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>3.861499999999999</v>
+        <v>15.4462</v>
       </c>
       <c r="Q7" t="n">
-        <v>-15.2532</v>
+        <v>-28.3828</v>
       </c>
       <c r="R7" t="n">
-        <v>19.1147</v>
+        <v>43.8289</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.745</v>
+        <v>-1.2548</v>
       </c>
       <c r="T7" t="n">
-        <v>-3.0649</v>
+        <v>3.5218</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6803000000000001</v>
+        <v>-4.7762</v>
       </c>
       <c r="V7" t="n">
-        <v>10.3126</v>
+        <v>6.905</v>
       </c>
       <c r="W7" t="n">
-        <v>12.6776</v>
+        <v>19.4171</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.365</v>
+        <v>-12.5121</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. MOLINA HERRERA</t>
+          <t>J. GARCIA CABRERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>15.1119</v>
+        <v>14.4813</v>
       </c>
       <c r="E8" t="n">
-        <v>1.606</v>
+        <v>1.2564</v>
       </c>
       <c r="F8" t="n">
-        <v>13.5058</v>
+        <v>13.2248</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1151</v>
+        <v>16.3661</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2684000000000006</v>
+        <v>14.4871</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3837000000000006</v>
+        <v>1.8791</v>
       </c>
       <c r="J8" t="n">
-        <v>11.433</v>
+        <v>18.5834</v>
       </c>
       <c r="K8" t="n">
-        <v>8.640899999999998</v>
+        <v>17.7431</v>
       </c>
       <c r="L8" t="n">
-        <v>2.7924</v>
+        <v>0.8404000000000004</v>
       </c>
       <c r="M8" t="n">
-        <v>-11.3177</v>
+        <v>-2.2171</v>
       </c>
       <c r="N8" t="n">
-        <v>-8.9093</v>
+        <v>-3.2559</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.4086</v>
+        <v>1.0386</v>
       </c>
       <c r="P8" t="n">
-        <v>1.158600000000001</v>
+        <v>19.6936</v>
       </c>
       <c r="Q8" t="n">
-        <v>-35.9128</v>
+        <v>-20.0804</v>
       </c>
       <c r="R8" t="n">
-        <v>37.0711</v>
+        <v>39.7738</v>
       </c>
       <c r="S8" t="n">
-        <v>6.5546</v>
+        <v>-7.867900000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>4.268000000000001</v>
+        <v>-1.1725</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2864</v>
+        <v>-6.6953</v>
       </c>
       <c r="V8" t="n">
-        <v>7.2836</v>
+        <v>-13.7111</v>
       </c>
       <c r="W8" t="n">
-        <v>21.8172</v>
+        <v>3.926</v>
       </c>
       <c r="X8" t="n">
-        <v>-14.5337</v>
+        <v>-17.6371</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. RAMOS BELASTEGUI</t>
+          <t>M. MOLINA HERRERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>1.192900000000001</v>
+        <v>12.1987</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.4646</v>
+        <v>-0.9451000000000009</v>
       </c>
       <c r="F9" t="n">
-        <v>7.6574</v>
+        <v>13.1442</v>
       </c>
       <c r="G9" t="n">
-        <v>22.6553</v>
+        <v>0.1151</v>
       </c>
       <c r="H9" t="n">
-        <v>7.3391</v>
+        <v>-0.2684000000000006</v>
       </c>
       <c r="I9" t="n">
-        <v>15.3163</v>
+        <v>0.3837000000000006</v>
       </c>
       <c r="J9" t="n">
-        <v>28.9123</v>
+        <v>11.433</v>
       </c>
       <c r="K9" t="n">
-        <v>15.2135</v>
+        <v>8.640899999999998</v>
       </c>
       <c r="L9" t="n">
-        <v>13.6985</v>
+        <v>2.7924</v>
       </c>
       <c r="M9" t="n">
-        <v>-6.257300000000001</v>
+        <v>-11.3177</v>
       </c>
       <c r="N9" t="n">
-        <v>-7.8745</v>
+        <v>-8.9093</v>
       </c>
       <c r="O9" t="n">
-        <v>1.6171</v>
+        <v>-2.4086</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5446</v>
+        <v>1.158600000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-37.2644</v>
+        <v>-35.9128</v>
       </c>
       <c r="R9" t="n">
-        <v>35.7194</v>
+        <v>37.0711</v>
       </c>
       <c r="S9" t="n">
-        <v>-16.5483</v>
+        <v>3.6419</v>
       </c>
       <c r="T9" t="n">
-        <v>-7.1499</v>
+        <v>1.7174</v>
       </c>
       <c r="U9" t="n">
-        <v>-9.398199999999999</v>
+        <v>1.9248</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.3694</v>
+        <v>7.2836</v>
       </c>
       <c r="W9" t="n">
-        <v>9.037000000000001</v>
+        <v>21.8172</v>
       </c>
       <c r="X9" t="n">
-        <v>-12.4066</v>
+        <v>-14.5337</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. GARCIA CABRERA</t>
+          <t>E. RAMOS BELASTEGUI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>1.126300000000001</v>
+        <v>9.370999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.831700000000001</v>
+        <v>-1.265799999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>5.9579</v>
+        <v>10.6366</v>
       </c>
       <c r="G10" t="n">
-        <v>16.3661</v>
+        <v>22.6553</v>
       </c>
       <c r="H10" t="n">
-        <v>14.4871</v>
+        <v>7.3391</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8791</v>
+        <v>15.3163</v>
       </c>
       <c r="J10" t="n">
-        <v>18.5834</v>
+        <v>28.9123</v>
       </c>
       <c r="K10" t="n">
-        <v>17.7431</v>
+        <v>15.2135</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8404000000000004</v>
+        <v>13.6985</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2171</v>
+        <v>-6.257300000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.2559</v>
+        <v>-7.8745</v>
       </c>
       <c r="O10" t="n">
-        <v>1.0386</v>
+        <v>1.6171</v>
       </c>
       <c r="P10" t="n">
-        <v>19.6936</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q10" t="n">
-        <v>-20.0804</v>
+        <v>-37.2644</v>
       </c>
       <c r="R10" t="n">
-        <v>39.7738</v>
+        <v>35.7194</v>
       </c>
       <c r="S10" t="n">
-        <v>-21.2231</v>
+        <v>-8.3703</v>
       </c>
       <c r="T10" t="n">
-        <v>-7.2613</v>
+        <v>-1.9512</v>
       </c>
       <c r="U10" t="n">
-        <v>-13.9617</v>
+        <v>-6.4193</v>
       </c>
       <c r="V10" t="n">
-        <v>-13.7111</v>
+        <v>-3.3694</v>
       </c>
       <c r="W10" t="n">
-        <v>3.926</v>
+        <v>9.037000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-17.6371</v>
+        <v>-12.4066</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1848</v>
+        <v>0.4895</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1104</v>
+        <v>-0.0069</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2951</v>
+        <v>0.4964</v>
       </c>
       <c r="G11" t="n">
         <v>0.8962</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7115</v>
+        <v>-0.4068</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1104</v>
+        <v>-0.0069</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6011</v>
+        <v>-0.3998</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. RIVERA RODRÍGUEZ</t>
+          <t>J. ORAMAS MARTEL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2584</v>
+        <v>0.01040000000000019</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9767</v>
+        <v>1.0769</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.235</v>
+        <v>-1.0663</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4521</v>
+        <v>3.0369</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1997</v>
+        <v>-1.8009</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2524</v>
+        <v>4.838100000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>2.6664</v>
+        <v>8.202599999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0621</v>
+        <v>2.9619</v>
       </c>
       <c r="L12" t="n">
-        <v>2.6043</v>
+        <v>5.2406</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2143</v>
+        <v>-5.1657</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1376</v>
+        <v>-4.763</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3519</v>
+        <v>-0.4029000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1931</v>
+        <v>-11.0056</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1931</v>
+        <v>11.5846</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-3.5307</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4966</v>
+        <v>-0.3747</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3144</v>
+        <v>-3.1562</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.8995</v>
+        <v>-0.07499999999999996</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>4.2542</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8995</v>
+        <v>-4.3293</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. RODRIGO HERNÁNDEZ</t>
+          <t>J. RIVERA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.1714</v>
+        <v>-0.006</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.9102999999999999</v>
+        <v>2.0801</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2611</v>
+        <v>-2.0861</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.9518</v>
+        <v>1.4521</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2276</v>
+        <v>0.1997</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2758</v>
+        <v>1.2524</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6066999999999999</v>
+        <v>2.6664</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6066999999999999</v>
+        <v>0.0621</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.6043</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3451</v>
+        <v>-1.2143</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6209</v>
+        <v>0.1376</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2758</v>
+        <v>-1.3519</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5792999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5792999999999999</v>
+        <v>0.1931</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5132</v>
+        <v>-0.5586</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3036</v>
+        <v>-0.3932</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2095</v>
+        <v>-0.1654</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2856</v>
+        <v>-0.8995</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2856</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. LLAMAS AFONSO</t>
+          <t>J. RODRIGO HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.8551</v>
+        <v>-0.9686</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8343</v>
+        <v>-0.8068</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0208</v>
+        <v>-0.1618</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.5517</v>
+        <v>-0.9518</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1862</v>
+        <v>-1.2276</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.3654</v>
+        <v>0.2758</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6688</v>
+        <v>-0.6066999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0207</v>
+        <v>-0.6066999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6895</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8829</v>
+        <v>-0.3451</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2069</v>
+        <v>-0.6209</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0.2758</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.5792999999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>0.5792999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3034</v>
+        <v>-0.3104</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1655</v>
+        <v>-0.2001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1379</v>
+        <v>-0.1102</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SANSON FIGUEROA</t>
+          <t>G. CAMPOS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.9768</v>
+        <v>-1.5998</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2784</v>
+        <v>-2.4983</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6984</v>
+        <v>0.8986999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4785</v>
+        <v>-5.1339</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8274</v>
+        <v>-0.5314000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6511</v>
+        <v>-4.6027</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.8023</v>
+        <v>-5.3109</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.9651</v>
+        <v>0.1597000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1628</v>
+        <v>-5.4706</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6761</v>
+        <v>0.1768999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1377</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8138</v>
+        <v>0.8679999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5792</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.8616</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5792</v>
+        <v>3.6685</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4357</v>
+        <v>-0.2412000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5239</v>
+        <v>1.1922</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0882</v>
+        <v>-1.4335</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.5133</v>
+        <v>3.9687</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>5.482</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.5133</v>
+        <v>-1.5132</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. CAMPOS RODRIGUEZ</t>
+          <t>F. LLAMAS AFONSO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.0148</v>
+        <v>-1.6965</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.8637</v>
+        <v>-0.6757</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8491999999999998</v>
+        <v>-1.0208</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.1339</v>
+        <v>-1.5517</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5314000000000001</v>
+        <v>-0.1862</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.6027</v>
+        <v>-1.3654</v>
       </c>
       <c r="J16" t="n">
-        <v>-5.3109</v>
+        <v>-0.6688</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1597000000000001</v>
+        <v>0.0207</v>
       </c>
       <c r="L16" t="n">
-        <v>-5.4706</v>
+        <v>-0.6895</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1768999999999999</v>
+        <v>-0.8829</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.2069</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8679999999999999</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.8616</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.6685</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6563999999999999</v>
+        <v>-0.1448</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8268000000000002</v>
+        <v>-0.0069</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.483</v>
+        <v>-0.1379</v>
       </c>
       <c r="V16" t="n">
-        <v>3.9687</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>5.482</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.5132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. DE LA ROSA ALVENTOSA</t>
+          <t>M. SANSON FIGUEROA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.2519</v>
+        <v>-2.1092</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.3868</v>
+        <v>-0.4853</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8651</v>
+        <v>-1.6239</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.7602</v>
+        <v>-1.4785</v>
       </c>
       <c r="H17" t="n">
-        <v>0.03390000000000004</v>
+        <v>-0.8274</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.7941</v>
+        <v>-0.6511</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.2279</v>
+        <v>-0.8023</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4486</v>
+        <v>-0.9651</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.6766</v>
+        <v>0.1628</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5323</v>
+        <v>-0.6761</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4146</v>
+        <v>0.1377</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1175</v>
+        <v>-0.8138</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5447</v>
+        <v>0.5792</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5447</v>
+        <v>0.5792</v>
       </c>
       <c r="S17" t="n">
-        <v>-3.1223</v>
+        <v>0.3034</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1589</v>
+        <v>0.3171</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.9635</v>
+        <v>-0.0137</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9139</v>
+        <v>-1.5133</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.9139</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. ORAMAS MARTEL</t>
+          <t>E. DE LA ROSA ALVENTOSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>-6.2125</v>
+        <v>-4.3156</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.7705</v>
+        <v>-3.0766</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.4419</v>
+        <v>-1.239</v>
       </c>
       <c r="G18" t="n">
-        <v>3.0369</v>
+        <v>-2.7602</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8009</v>
+        <v>0.03390000000000004</v>
       </c>
       <c r="I18" t="n">
-        <v>4.838100000000001</v>
+        <v>-2.7941</v>
       </c>
       <c r="J18" t="n">
-        <v>8.202599999999999</v>
+        <v>-2.2279</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9619</v>
+        <v>0.4486</v>
       </c>
       <c r="L18" t="n">
-        <v>5.2406</v>
+        <v>-2.6766</v>
       </c>
       <c r="M18" t="n">
-        <v>-5.1657</v>
+        <v>-0.5323</v>
       </c>
       <c r="N18" t="n">
-        <v>-4.763</v>
+        <v>-0.4146</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4029000000000001</v>
+        <v>-0.1175</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5792</v>
+        <v>1.5447</v>
       </c>
       <c r="Q18" t="n">
-        <v>-11.0056</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>11.5846</v>
+        <v>1.5447</v>
       </c>
       <c r="S18" t="n">
-        <v>-9.7537</v>
+        <v>-2.1861</v>
       </c>
       <c r="T18" t="n">
-        <v>-4.2221</v>
+        <v>-0.8486</v>
       </c>
       <c r="U18" t="n">
-        <v>-5.5314</v>
+        <v>-1.3374</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.07499999999999996</v>
+        <v>-0.9139</v>
       </c>
       <c r="W18" t="n">
-        <v>4.2542</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-4.3293</v>
+        <v>-0.9139</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. LORENZO MEDINA</t>
+          <t>S. RODRIGUEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-7.015499999999999</v>
+        <v>-6.561699999999998</v>
       </c>
       <c r="E19" t="n">
-        <v>3.5848</v>
+        <v>-3.8513</v>
       </c>
       <c r="F19" t="n">
-        <v>-10.6002</v>
+        <v>-2.7104</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2562</v>
+        <v>-11.7072</v>
       </c>
       <c r="H19" t="n">
-        <v>3.399100000000001</v>
+        <v>-8.508600000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.654800000000001</v>
+        <v>-3.198700000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>8.3149</v>
+        <v>9.7887</v>
       </c>
       <c r="K19" t="n">
-        <v>6.85</v>
+        <v>3.5072</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4651</v>
+        <v>6.281899999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-9.571</v>
+        <v>-21.4959</v>
       </c>
       <c r="N19" t="n">
-        <v>-3.4506</v>
+        <v>-12.0156</v>
       </c>
       <c r="O19" t="n">
-        <v>-6.1197</v>
+        <v>-9.480599999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>2.7032</v>
+        <v>19.5009</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.4063</v>
+        <v>-22.0112</v>
       </c>
       <c r="R19" t="n">
-        <v>8.109500000000001</v>
+        <v>41.5115</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0309</v>
+        <v>-1.5439</v>
       </c>
       <c r="T19" t="n">
-        <v>2.6455</v>
+        <v>-1.9667</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.6144</v>
+        <v>0.4228</v>
       </c>
       <c r="V19" t="n">
-        <v>-9.4932</v>
+        <v>-12.8113</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.9694</v>
+        <v>10.3373</v>
       </c>
       <c r="X19" t="n">
-        <v>-7.5239</v>
+        <v>-23.1487</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>-11.1103</v>
+        <v>-7.417199999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.854800000000001</v>
+        <v>-3.5868</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.255599999999999</v>
+        <v>-3.8306</v>
       </c>
       <c r="G20" t="n">
         <v>-3.8897</v>
@@ -2014,13 +2014,13 @@
         <v>11.1986</v>
       </c>
       <c r="S20" t="n">
-        <v>-6.7133</v>
+        <v>-3.0203</v>
       </c>
       <c r="T20" t="n">
-        <v>-4.8844</v>
+        <v>-1.6163</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.8288</v>
+        <v>-1.4041</v>
       </c>
       <c r="V20" t="n">
         <v>-3.7897</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ HERNANDEZ</t>
+          <t>J. LORENZO MEDINA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,70 +2044,70 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>-14.919</v>
+        <v>-8.536099999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-10.2224</v>
+        <v>1.013</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.6962</v>
+        <v>-9.549199999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-11.7072</v>
+        <v>-1.2562</v>
       </c>
       <c r="H21" t="n">
-        <v>-8.508600000000001</v>
+        <v>3.399100000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.198700000000001</v>
+        <v>-4.654800000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>9.7887</v>
+        <v>8.3149</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5072</v>
+        <v>6.85</v>
       </c>
       <c r="L21" t="n">
-        <v>6.281899999999999</v>
+        <v>1.4651</v>
       </c>
       <c r="M21" t="n">
-        <v>-21.4959</v>
+        <v>-9.571</v>
       </c>
       <c r="N21" t="n">
-        <v>-12.0156</v>
+        <v>-3.4506</v>
       </c>
       <c r="O21" t="n">
-        <v>-9.480599999999999</v>
+        <v>-6.1197</v>
       </c>
       <c r="P21" t="n">
-        <v>19.5009</v>
+        <v>2.7032</v>
       </c>
       <c r="Q21" t="n">
-        <v>-22.0112</v>
+        <v>-5.4063</v>
       </c>
       <c r="R21" t="n">
-        <v>41.5115</v>
+        <v>8.109500000000001</v>
       </c>
       <c r="S21" t="n">
-        <v>-9.901199999999999</v>
+        <v>-0.4898999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-8.337899999999999</v>
+        <v>0.07369999999999993</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.5632</v>
+        <v>-0.5634999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-12.8113</v>
+        <v>-9.4932</v>
       </c>
       <c r="W21" t="n">
-        <v>10.3373</v>
+        <v>-1.9694</v>
       </c>
       <c r="X21" t="n">
-        <v>-23.1487</v>
+        <v>-7.5239</v>
       </c>
     </row>
     <row r="22">
@@ -2125,22 +2125,22 @@
         <v>26</v>
       </c>
       <c r="D22" t="n">
-        <v>205.0023</v>
+        <v>229.1373</v>
       </c>
       <c r="E22" t="n">
-        <v>102.1946</v>
+        <v>110.4706</v>
       </c>
       <c r="F22" t="n">
-        <v>102.8086</v>
+        <v>118.6664</v>
       </c>
       <c r="G22" t="n">
         <v>111.1725</v>
       </c>
       <c r="H22" t="n">
-        <v>77.60490000000001</v>
+        <v>77.6049</v>
       </c>
       <c r="I22" t="n">
-        <v>33.56849999999999</v>
+        <v>33.56850000000001</v>
       </c>
       <c r="J22" t="n">
         <v>271.2024</v>
@@ -2149,7 +2149,7 @@
         <v>199.1439</v>
       </c>
       <c r="L22" t="n">
-        <v>72.05889999999999</v>
+        <v>72.05890000000001</v>
       </c>
       <c r="M22" t="n">
         <v>-160.0297</v>
@@ -2164,22 +2164,22 @@
         <v>102.3311</v>
       </c>
       <c r="Q22" t="n">
-        <v>-354.3012</v>
+        <v>-354.3011999999999</v>
       </c>
       <c r="R22" t="n">
         <v>456.629</v>
       </c>
       <c r="S22" t="n">
-        <v>-35.30240000000001</v>
+        <v>-11.1671</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.745899999999996</v>
+        <v>6.531900000000002</v>
       </c>
       <c r="U22" t="n">
-        <v>-33.5554</v>
+        <v>-17.6977</v>
       </c>
       <c r="V22" t="n">
-        <v>26.8005</v>
+        <v>26.80049999999999</v>
       </c>
       <c r="W22" t="n">
         <v>187.035</v>
